--- a/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report.Overview.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report.Overview.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\23H2\Expand\Install\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08A0F72-9E42-4195-BF3A-28BC493A426B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A0E6A8-78AB-444D-98CA-9C75E200EF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report.Overview" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="117">
   <si>
     <t>Verify if it is published by Yi</t>
   </si>
@@ -612,6 +612,19 @@
   </si>
   <si>
     <t>Download the full report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+en-US
+ar-EG
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.22621.2428
+Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.22621.2428
+Microsoft-Windows-LanguageFeatures-TextToSpeech-ar-eg-Package~31bf3856ad364e35~amd64~~10.0.22621.2428
+</t>
   </si>
 </sst>
 </file>
@@ -2012,24 +2025,24 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N70"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="84.69140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="50.3828125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="20.53515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="16.69140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="120.69140625" style="3" customWidth="1"/>
-    <col min="9" max="11" width="16.69140625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="25.69140625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="16.69140625" style="7" customWidth="1"/>
-    <col min="14" max="14" width="2.69140625" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.15234375" style="1" hidden="1"/>
+    <col min="1" max="1" width="2.6640625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="84.6640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="50.3984375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.53125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="120.6640625" style="3" customWidth="1"/>
+    <col min="9" max="11" width="16.6640625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="25.6640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" style="7" customWidth="1"/>
+    <col min="14" max="14" width="2.6640625" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.1328125" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2044,7 +2057,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:14" ht="80.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" ht="80.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="1"/>
       <c r="C2" s="20" t="s">
         <v>46</v>
@@ -2063,7 +2076,7 @@
       </c>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -2077,7 +2090,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -2090,7 +2103,7 @@
       <c r="K4" s="10"/>
       <c r="L4" s="23"/>
     </row>
-    <row r="5" spans="1:14" ht="62.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" ht="62.85" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
         <v>7</v>
@@ -2127,7 +2140,7 @@
       </c>
       <c r="N5" s="7"/>
     </row>
-    <row r="6" spans="1:14" ht="285.45" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" ht="283.5" x14ac:dyDescent="0.45">
       <c r="B6" s="13"/>
       <c r="C6" s="3">
         <v>1</v>
@@ -2160,7 +2173,7 @@
       <c r="M6" s="15"/>
       <c r="N6" s="7"/>
     </row>
-    <row r="7" spans="1:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B7" s="13"/>
       <c r="C7" s="3">
         <v>2</v>
@@ -2175,10 +2188,10 @@
         <v>6</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="I7" s="13">
         <v>1</v>
@@ -2195,7 +2208,7 @@
       <c r="M7" s="15"/>
       <c r="N7" s="7"/>
     </row>
-    <row r="8" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B8" s="13"/>
       <c r="C8" s="3">
         <v>3</v>
@@ -2230,7 +2243,7 @@
       <c r="M8" s="15"/>
       <c r="N8" s="7"/>
     </row>
-    <row r="9" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B9" s="13"/>
       <c r="C9" s="3">
         <v>4</v>
@@ -2263,7 +2276,7 @@
       <c r="M9" s="15"/>
       <c r="N9" s="7"/>
     </row>
-    <row r="10" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B10" s="13"/>
       <c r="C10" s="3">
         <v>5</v>
@@ -2298,7 +2311,7 @@
       <c r="M10" s="15"/>
       <c r="N10" s="7"/>
     </row>
-    <row r="11" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B11" s="13"/>
       <c r="C11" s="3">
         <v>6</v>
@@ -2331,7 +2344,7 @@
       <c r="M11" s="15"/>
       <c r="N11" s="7"/>
     </row>
-    <row r="12" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B12" s="13"/>
       <c r="C12" s="3">
         <v>7</v>
@@ -2366,7 +2379,7 @@
       <c r="M12" s="13"/>
       <c r="N12" s="7"/>
     </row>
-    <row r="13" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B13" s="13"/>
       <c r="C13" s="3">
         <v>8</v>
@@ -2399,7 +2412,7 @@
       <c r="M13" s="13"/>
       <c r="N13" s="7"/>
     </row>
-    <row r="14" spans="1:14" ht="253.75" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:14" ht="252" x14ac:dyDescent="0.45">
       <c r="B14" s="13"/>
       <c r="C14" s="3">
         <v>9</v>
@@ -2432,7 +2445,7 @@
       <c r="M14" s="13"/>
       <c r="N14" s="7"/>
     </row>
-    <row r="15" spans="1:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B15" s="13"/>
       <c r="C15" s="3">
         <v>10</v>
@@ -2465,7 +2478,7 @@
       <c r="M15" s="13"/>
       <c r="N15" s="7"/>
     </row>
-    <row r="16" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B16" s="13"/>
       <c r="C16" s="3">
         <v>11</v>
@@ -2498,7 +2511,7 @@
       <c r="M16" s="13"/>
       <c r="N16" s="7"/>
     </row>
-    <row r="17" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B17" s="13"/>
       <c r="C17" s="3">
         <v>12</v>
@@ -2531,7 +2544,7 @@
       <c r="M17" s="13"/>
       <c r="N17" s="7"/>
     </row>
-    <row r="18" spans="1:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B18" s="13"/>
       <c r="C18" s="3">
         <v>13</v>
@@ -2566,7 +2579,7 @@
       <c r="M18" s="13"/>
       <c r="N18" s="7"/>
     </row>
-    <row r="19" spans="1:14" ht="253.75" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:14" ht="252" x14ac:dyDescent="0.45">
       <c r="B19" s="13"/>
       <c r="C19" s="3">
         <v>14</v>
@@ -2599,7 +2612,7 @@
       <c r="M19" s="13"/>
       <c r="N19" s="7"/>
     </row>
-    <row r="20" spans="1:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B20" s="13"/>
       <c r="C20" s="3">
         <v>15</v>
@@ -2634,7 +2647,7 @@
       <c r="M20" s="13"/>
       <c r="N20" s="7"/>
     </row>
-    <row r="21" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B21" s="13"/>
       <c r="C21" s="3">
         <v>16</v>
@@ -2667,7 +2680,7 @@
       <c r="M21" s="13"/>
       <c r="N21" s="7"/>
     </row>
-    <row r="22" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B22" s="13"/>
       <c r="C22" s="3">
         <v>17</v>
@@ -2700,7 +2713,7 @@
       <c r="M22" s="13"/>
       <c r="N22" s="7"/>
     </row>
-    <row r="23" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B23" s="13"/>
       <c r="C23" s="3">
         <v>18</v>
@@ -2733,7 +2746,7 @@
       <c r="M23" s="13"/>
       <c r="N23" s="7"/>
     </row>
-    <row r="24" spans="1:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B24" s="13"/>
       <c r="C24" s="3">
         <v>19</v>
@@ -2766,7 +2779,7 @@
       <c r="M24" s="13"/>
       <c r="N24" s="7"/>
     </row>
-    <row r="25" spans="1:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B25" s="13"/>
       <c r="C25" s="3">
         <v>20</v>
@@ -2799,7 +2812,7 @@
       <c r="M25" s="13"/>
       <c r="N25" s="7"/>
     </row>
-    <row r="26" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B26" s="13"/>
       <c r="C26" s="3">
         <v>21</v>
@@ -2832,7 +2845,7 @@
       <c r="M26" s="13"/>
       <c r="N26" s="7"/>
     </row>
-    <row r="27" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B27" s="13"/>
       <c r="C27" s="3">
         <v>22</v>
@@ -2865,7 +2878,7 @@
       <c r="M27" s="13"/>
       <c r="N27" s="7"/>
     </row>
-    <row r="28" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="s">
         <v>82</v>
       </c>
@@ -2901,7 +2914,7 @@
       <c r="M28" s="13"/>
       <c r="N28" s="7"/>
     </row>
-    <row r="29" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B29" s="13"/>
       <c r="C29" s="3">
         <v>24</v>
@@ -2934,7 +2947,7 @@
       <c r="M29" s="13"/>
       <c r="N29" s="7"/>
     </row>
-    <row r="30" spans="1:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B30" s="13"/>
       <c r="C30" s="3">
         <v>25</v>
@@ -2967,7 +2980,7 @@
       <c r="M30" s="13"/>
       <c r="N30" s="7"/>
     </row>
-    <row r="31" spans="1:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B31" s="13"/>
       <c r="C31" s="3">
         <v>26</v>
@@ -3000,7 +3013,7 @@
       <c r="M31" s="13"/>
       <c r="N31" s="7"/>
     </row>
-    <row r="32" spans="1:14" ht="253.75" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:14" ht="252" x14ac:dyDescent="0.45">
       <c r="B32" s="13"/>
       <c r="C32" s="3">
         <v>27</v>
@@ -3033,7 +3046,7 @@
       <c r="M32" s="13"/>
       <c r="N32" s="7"/>
     </row>
-    <row r="33" spans="2:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B33" s="13"/>
       <c r="C33" s="3">
         <v>28</v>
@@ -3066,7 +3079,7 @@
       <c r="M33" s="13"/>
       <c r="N33" s="7"/>
     </row>
-    <row r="34" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B34" s="13"/>
       <c r="C34" s="3">
         <v>29</v>
@@ -3101,7 +3114,7 @@
       <c r="M34" s="13"/>
       <c r="N34" s="7"/>
     </row>
-    <row r="35" spans="2:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B35" s="13"/>
       <c r="C35" s="3">
         <v>30</v>
@@ -3134,7 +3147,7 @@
       <c r="M35" s="13"/>
       <c r="N35" s="7"/>
     </row>
-    <row r="36" spans="2:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B36" s="13"/>
       <c r="C36" s="3">
         <v>31</v>
@@ -3167,7 +3180,7 @@
       <c r="M36" s="13"/>
       <c r="N36" s="7"/>
     </row>
-    <row r="37" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B37" s="13"/>
       <c r="C37" s="3">
         <v>32</v>
@@ -3200,7 +3213,7 @@
       <c r="M37" s="13"/>
       <c r="N37" s="7"/>
     </row>
-    <row r="38" spans="2:14" ht="237.9" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:14" ht="236.25" x14ac:dyDescent="0.45">
       <c r="B38" s="13"/>
       <c r="C38" s="3">
         <v>33</v>
@@ -3233,7 +3246,7 @@
       <c r="M38" s="13"/>
       <c r="N38" s="7"/>
     </row>
-    <row r="39" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B39" s="13"/>
       <c r="C39" s="3">
         <v>34</v>
@@ -3268,7 +3281,7 @@
       <c r="M39" s="13"/>
       <c r="N39" s="7"/>
     </row>
-    <row r="40" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B40" s="13"/>
       <c r="C40" s="3">
         <v>35</v>
@@ -3301,7 +3314,7 @@
       <c r="M40" s="13"/>
       <c r="N40" s="7"/>
     </row>
-    <row r="41" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B41" s="13"/>
       <c r="C41" s="3">
         <v>36</v>
@@ -3336,7 +3349,7 @@
       <c r="M41" s="13"/>
       <c r="N41" s="7"/>
     </row>
-    <row r="42" spans="2:14" ht="158.6" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:14" ht="157.5" x14ac:dyDescent="0.45">
       <c r="B42" s="13"/>
       <c r="C42" s="3">
         <v>37</v>
@@ -3369,7 +3382,7 @@
       <c r="M42" s="13"/>
       <c r="N42" s="7"/>
     </row>
-    <row r="43" spans="2:14" ht="142.75" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:14" ht="141.75" x14ac:dyDescent="0.45">
       <c r="B43" s="13"/>
       <c r="C43" s="3">
         <v>38</v>
@@ -3404,7 +3417,7 @@
       <c r="M43" s="13"/>
       <c r="N43" s="7"/>
     </row>
-    <row r="44" spans="2:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
       <c r="E44" s="14"/>
@@ -3416,7 +3429,7 @@
       <c r="K44" s="13"/>
       <c r="L44" s="13"/>
     </row>
-    <row r="45" spans="2:14" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:14" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B45" s="16"/>
       <c r="C45" s="25" t="s">
         <v>2</v>
@@ -3426,7 +3439,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B46" s="18"/>
       <c r="C46" s="24" t="s">
         <v>0</v>
@@ -3443,7 +3456,7 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
     </row>
-    <row r="47" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="19"/>
       <c r="C47" s="24" t="s">
         <v>1</v>
@@ -3460,7 +3473,7 @@
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
     </row>
-    <row r="48" spans="2:14" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:14" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -3472,7 +3485,7 @@
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
     </row>
-    <row r="49" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
@@ -3480,7 +3493,7 @@
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
@@ -3493,7 +3506,7 @@
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
     </row>
-    <row r="51" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -3506,7 +3519,7 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
     </row>
-    <row r="52" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
@@ -3519,7 +3532,7 @@
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
     </row>
-    <row r="53" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
@@ -3532,7 +3545,7 @@
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
     </row>
-    <row r="54" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
@@ -3545,7 +3558,7 @@
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
     </row>
-    <row r="55" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
@@ -3558,7 +3571,7 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
     </row>
-    <row r="56" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -3571,7 +3584,7 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
     </row>
-    <row r="57" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
@@ -3584,7 +3597,7 @@
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
     </row>
-    <row r="58" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
@@ -3597,7 +3610,7 @@
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
     </row>
-    <row r="59" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
@@ -3610,7 +3623,7 @@
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
     </row>
-    <row r="60" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
@@ -3623,7 +3636,7 @@
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
     </row>
-    <row r="61" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
@@ -3636,7 +3649,7 @@
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
     </row>
-    <row r="62" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
@@ -3649,7 +3662,7 @@
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
     </row>
-    <row r="63" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
@@ -3662,7 +3675,7 @@
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
     </row>
-    <row r="64" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
@@ -3675,7 +3688,7 @@
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
     </row>
-    <row r="65" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
@@ -3688,7 +3701,7 @@
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
     </row>
-    <row r="66" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
@@ -3701,7 +3714,7 @@
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
     </row>
-    <row r="67" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
@@ -3714,7 +3727,7 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
     </row>
-    <row r="68" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
@@ -3727,7 +3740,7 @@
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
     </row>
-    <row r="69" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
@@ -3740,7 +3753,7 @@
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
     </row>
-    <row r="70" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="2:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
